--- a/AI_Log/PRJ301_SE20C_Group6.xlsx
+++ b/AI_Log/PRJ301_SE20C_Group6.xlsx
@@ -1,29 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QUOC VUONG\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198ED894-669F-463F-BDF7-EAA9B791B59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6A96F1-140C-403F-A15B-FE4F780C2EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
     <sheet name="1. Week 1" sheetId="2" r:id="rId2"/>
     <sheet name="2. Week 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Instruction" sheetId="4" r:id="rId4"/>
+    <sheet name="3. Week 3" sheetId="5" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="7" r:id="rId5"/>
+    <sheet name="4.Week 5" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 6" sheetId="8" r:id="rId7"/>
+    <sheet name="Week 7" sheetId="9" r:id="rId8"/>
+    <sheet name="Week 8" sheetId="10" r:id="rId9"/>
+    <sheet name="Instruction" sheetId="4" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="290">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -198,221 +204,710 @@
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
   </si>
   <si>
-    <t>Requirements Analysis</t>
-  </si>
-  <si>
-    <t>Design the data flow for the Git Analytics feature</t>
+    <t>Technical Foundation</t>
+  </si>
+  <si>
+    <t>Review Tomcat deployment and servlet-container request flow</t>
   </si>
   <si>
     <t>ChatGPT</t>
   </si>
   <si>
-    <t>Proposed a 5-step workflow: Enter Repository URL → Crawl Git Data → Calculate Contribution Score → Store in Database → Display Dashboard</t>
-  </si>
-  <si>
-    <t>Checked whether the proposed workflow matched the actual system requirements and modified the flow when necessary</t>
-  </si>
-  <si>
-    <t>5 main workflow steps</t>
-  </si>
-  <si>
-    <t>The workflow may need to be adjusted according to the actual system architecture</t>
-  </si>
-  <si>
-    <t>Identify where lecturer/student information and CRUD operations should be handled</t>
-  </si>
-  <si>
-    <t>Suggested handling CRUD through the Controller → Service → DAO → Database layers</t>
-  </si>
-  <si>
-    <t>Checked whether Add, Update, Delete, and View operations matched the actual student/class management requirements</t>
-  </si>
-  <si>
-    <t>CRUD operations for student/class data</t>
-  </si>
-  <si>
-    <t>AI does not have complete knowledge of the project's current database and business rules</t>
-  </si>
-  <si>
-    <t>System Design</t>
-  </si>
-  <si>
-    <t>Develop the Contribution Score (%) formula</t>
-  </si>
-  <si>
-    <t>Proposed a formula based on Commit Count, Lines of Code Added/Deleted (LOC), Activity Regularity, and Pull Requests</t>
-  </si>
-  <si>
-    <t>Tested the formula using sample data and reviewed/adjusted the weighting of each criterion</t>
-  </si>
-  <si>
-    <t>4 contribution criteria</t>
-  </si>
-  <si>
-    <t>A high number of commits or LOC does not necessarily mean higher-quality or more meaningful contribution</t>
+    <t>Summarized how a Java web application is packaged as a WAR, deployed to Tomcat, and routed to a web endpoint.</t>
+  </si>
+  <si>
+    <t>Compared the outline with the project run guide, which specifies Apache Tomcat 9; deployment paths remain environment-dependent.</t>
+  </si>
+  <si>
+    <t>1 WAR deployment flow + 1 servlet-container request path</t>
+  </si>
+  <si>
+    <t>Tomcat configuration, Java version, and local paths vary between team machines.</t>
+  </si>
+  <si>
+    <t>Technical Foundation / System Design</t>
+  </si>
+  <si>
+    <t>Map the Servlet lifecycle and MVC2 responsibilities for AITA</t>
+  </si>
+  <si>
+    <t>Outlined the request lifecycle and separated Servlet Controller, business Service, DAO, and JSP View responsibilities.</t>
+  </si>
+  <si>
+    <t>Checked the proposed layers against the project architecture description and kept business rules out of JSP views.</t>
+  </si>
+  <si>
+    <t>4 MVC2 layers + 1 request lifecycle</t>
+  </si>
+  <si>
+    <t>Existing modules may not yet follow the proposed boundaries consistently.</t>
+  </si>
+  <si>
+    <t>Technical Foundation / Database</t>
+  </si>
+  <si>
+    <t>Summarize advanced JDBC practices for the SQL Server application</t>
+  </si>
+  <si>
+    <t>Prepared a JDBC checklist covering PreparedStatement, transaction boundaries, connection/resource cleanup, and SQL Server configuration.</t>
+  </si>
+  <si>
+    <t>Compared database assumptions with the project README, which identifies SQL Server; provider-specific syntax still needs review during implementation.</t>
+  </si>
+  <si>
+    <t>4 JDBC practices</t>
+  </si>
+  <si>
+    <t>Connection pooling, transaction isolation, and SQL Server driver settings are not established by this design note.</t>
   </si>
   <si>
     <t>Database Design</t>
   </si>
   <si>
-    <t>Design the database structure for Git Analytics</t>
-  </si>
-  <si>
-    <t>Proposed tables such as User, Class, Repository, Author, Commit, Pull Request, and Contribution Report, including PKs, FKs, and indexes</t>
-  </si>
-  <si>
-    <t>Reviewed primary keys, foreign keys, data types, relationships, and indexes to ensure they matched the project requirements</t>
-  </si>
-  <si>
-    <t>8 main database tables</t>
-  </si>
-  <si>
-    <t>Additional tables may be required as the system's business requirements become clearer</t>
+    <t>Draft the system ERD entity inventory for AITA (section 2.1)</t>
+  </si>
+  <si>
+    <t>Proposed a system ERD scope covering identity, courses/classes, submissions, Git repositories, commits, and contribution scores with key relationships.</t>
+  </si>
+  <si>
+    <t>Compared the entity scope with the course roadmap and the project description; exact cardinalities and existing table names remain to be confirmed by the team.</t>
+  </si>
+  <si>
+    <t>6 ERD subject areas + PK/FK relationship draft</t>
+  </si>
+  <si>
+    <t>A broad ERD can duplicate existing tables or miss constraints until reconciled with the current database.</t>
   </si>
   <si>
     <t>UI/UX Design</t>
   </si>
   <si>
-    <t>Design the lecturer Git Analytics Dashboard</t>
-  </si>
-  <si>
-    <t>Proposed a dashboard containing a Contribution Percentage Pie Chart, Commit-by-Date Bar Chart, and Commit History Table</t>
-  </si>
-  <si>
-    <t>Reviewed the layout and adjusted the components to improve readability and lecturer usability</t>
-  </si>
-  <si>
-    <t>2 main charts + data tables</t>
-  </si>
-  <si>
-    <t>AI-generated wireframes are only prototypes and require adjustment based on the actual UI</t>
-  </si>
-  <si>
-    <t>Risk Analysis</t>
-  </si>
-  <si>
-    <t>Identify Git cheating/free-riding behaviors</t>
-  </si>
-  <si>
-    <t>Suggested detecting spam commits, meaningless code, large last-minute commits, and other suspicious contribution patterns</t>
-  </si>
-  <si>
-    <t>Compared the proposed criteria with realistic Git behavior and considered how the system could avoid incorrectly flagging students</t>
-  </si>
-  <si>
-    <t>Multiple fraud-detection criteria</t>
-  </si>
-  <si>
-    <t>The system may produce false positives if it relies only on quantitative Git statistics</t>
-  </si>
-  <si>
-    <t>System Architecture / Implementation Design</t>
-  </si>
-  <si>
-    <t>Design the Java Web MVC project structure</t>
-  </si>
-  <si>
-    <t>Proposed a layered architecture: Servlet → Service → DAO → Database, with JSP as the View layer</t>
-  </si>
-  <si>
-    <t>Checked the folder structure and ensured that the design was compatible with Java 8, Servlet, JSP, JDBC, and Maven</t>
-  </si>
-  <si>
-    <t>4 main architectural layers</t>
-  </si>
-  <si>
-    <t>The suggested architecture may need modification to match the team's existing project structure</t>
-  </si>
-  <si>
-    <t>Implementation / Testing</t>
-  </si>
-  <si>
-    <t>Implement the Contribution Score Service and Unit Tests</t>
-  </si>
-  <si>
-    <t>Generated a ContributionScoreService, Mock Data, and JUnit 5 test cases for calculating student contribution percentages</t>
-  </si>
-  <si>
-    <t>Ran the Unit Tests, checked the calculated results, and modified the code when necessary</t>
-  </si>
-  <si>
-    <t>5 sample test cases</t>
-  </si>
-  <si>
-    <t>Mock Data does not represent real Git repository data and must eventually be replaced with actual Git API data</t>
-  </si>
-  <si>
-    <t>Implementation / Database</t>
-  </si>
-  <si>
-    <t>Create schema.sql and a JDBC Commit DAO</t>
-  </si>
-  <si>
-    <t>Generated SQL CREATE TABLE statements, Foreign Keys, Indexes, and a Java CommitDAO using JDBC PreparedStatement to store commit history in MySQL</t>
-  </si>
-  <si>
-    <t>Executed the SQL in MySQL, checked table relationships, and tested whether commit data could be inserted successfully</t>
-  </si>
-  <si>
-    <t>8 main tables + multiple FKs/Indexes</t>
-  </si>
-  <si>
-    <t>Database configuration, JDBC connection settings, and MySQL compatibility still need to be verified</t>
+    <t>Define lecturer and student journeys for the UI/UX prototype (section 2.2)</t>
+  </si>
+  <si>
+    <t>Drafted role-based screen flows for lecturer course/class management and Git contribution review, and for student course access and submission status.</t>
+  </si>
+  <si>
+    <t>Checked the flows against the two user roles in the project guide and separated lecturer-only functions from student views.</t>
+  </si>
+  <si>
+    <t>2 user roles + 2 primary journey flows</t>
+  </si>
+  <si>
+    <t>Prototype flows need user feedback and must match the final authorization rules.</t>
+  </si>
+  <si>
+    <t>Refine ERD keys and relationships for identity and course management</t>
+  </si>
+  <si>
+    <t>Suggested primary keys, foreign keys, and cardinalities for users, lecturer assignments, courses, classes, and student enrollment.</t>
+  </si>
+  <si>
+    <t>Reviewed the relationship choices against the roadmap and marked uncertain enrollment and lecturer-course rules for team confirmation.</t>
+  </si>
+  <si>
+    <t>5 core entity types + PK/FK/cardinality definitions</t>
+  </si>
+  <si>
+    <t>Incorrect cardinalities could grant access across courses or classes.</t>
+  </si>
+  <si>
+    <t>Database Design / JDBC</t>
+  </si>
+  <si>
+    <t>Map JDBC DAO queries to the approved ERD and SQL Server schema</t>
+  </si>
+  <si>
+    <t>Outlined DAO query responsibilities for loading course membership and Git Analytics records using parameterized SQL.</t>
+  </si>
+  <si>
+    <t>Checked that the proposal uses SQL Server-compatible JDBC assumptions and PreparedStatement rather than concatenated user input.</t>
+  </si>
+  <si>
+    <t>2 DAO query areas + 1 parameterization rule</t>
+  </si>
+  <si>
+    <t>Actual table and column names must be confirmed before SQL is used; query performance is not measured here.</t>
+  </si>
+  <si>
+    <t>Security / Identity Design</t>
+  </si>
+  <si>
+    <t>Design the JWT authentication flow for section 4.1.3</t>
+  </si>
+  <si>
+    <t>Drafted a token flow covering credential verification, signed token issuance, expiry, signature validation, and role/subject claims.</t>
+  </si>
+  <si>
+    <t>Compared the flow with the stated Identity scope and kept token validation on protected requests; storage and refresh policy remain design decisions.</t>
+  </si>
+  <si>
+    <t>1 authentication flow + 4 token checks</t>
+  </si>
+  <si>
+    <t>Token signing keys, storage, revocation, and CSRF exposure require explicit security decisions.</t>
+  </si>
+  <si>
+    <t>Prototype lecturer screens for course management and Git Analytics</t>
+  </si>
+  <si>
+    <t>Suggested lecturer screens for assigned courses/classes, student lists, and the FE-L-03 contribution dashboard.</t>
+  </si>
+  <si>
+    <t>Checked that the proposed screens distinguish course management from contribution review and avoid showing unassigned classes.</t>
+  </si>
+  <si>
+    <t>3 lecturer screen concepts</t>
+  </si>
+  <si>
+    <t>The interface must follow server-side authorization and may need changes after lecturer feedback.</t>
+  </si>
+  <si>
+    <t>Prototype student screens for course access and learning activity</t>
+  </si>
+  <si>
+    <t>Suggested student views for enrolled courses, course materials, assignment/submission status, and personal Git contribution summaries.</t>
+  </si>
+  <si>
+    <t>Compared the screen scope with the student role in the project guide and limited course content to the student’s enrolled classes.</t>
+  </si>
+  <si>
+    <t>4 student screen areas</t>
+  </si>
+  <si>
+    <t>Student-visible data must be filtered by enrollment on the API, not only hidden in the UI.</t>
+  </si>
+  <si>
+    <t>Peer Review 1 / Database Design</t>
+  </si>
+  <si>
+    <t>Review the system ERD structure, keys, and relationship constraints</t>
+  </si>
+  <si>
+    <t>Created a database-design review checklist for entity scope, normalization, PK/FK integrity, cardinality, and deletion/update behavior.</t>
+  </si>
+  <si>
+    <t>Aligned the checklist with Peer-Review 1’s database-design objective; record actual reviewer findings and agreed changes after the team review.</t>
+  </si>
+  <si>
+    <t>5 database review criteria</t>
+  </si>
+  <si>
+    <t>A checklist does not confirm that the ERD or schema has passed peer review.</t>
+  </si>
+  <si>
+    <t>Peer Review 1 / Security</t>
+  </si>
+  <si>
+    <t>Review JWT authentication design for section 4.1.3</t>
+  </si>
+  <si>
+    <t>Drafted review questions for token signature, expiry, issuer/audience, role claims, protected-route validation, and key handling.</t>
+  </si>
+  <si>
+    <t>Compared the questions with the JWT review scope and highlighted token storage and revocation as open decisions for the reviewers.</t>
+  </si>
+  <si>
+    <t>6 JWT security review checks</t>
+  </si>
+  <si>
+    <t>The selected JWT library and deployment key management are not verified by this design review.</t>
+  </si>
+  <si>
+    <t>Check identity and course-management access relationships</t>
+  </si>
+  <si>
+    <t>Outlined cases to review for lecturer-to-course assignments, student-to-class enrollment, and ownership of submission records.</t>
+  </si>
+  <si>
+    <t>Checked that the proposed cases cover the Identity and Course Management roadmap; authorization behavior must be confirmed against the final ERD.</t>
+  </si>
+  <si>
+    <t>3 access relationships</t>
+  </si>
+  <si>
+    <t>A correct schema alone cannot enforce every application-level access rule.</t>
+  </si>
+  <si>
+    <t>Peer Review 1 / Technical Design</t>
+  </si>
+  <si>
+    <t>Review JDBC and data-access assumptions against the ERD</t>
+  </si>
+  <si>
+    <t>Prepared a review checklist connecting JDBC DAO responsibilities to ERD keys, parameterized queries, and transaction boundaries.</t>
+  </si>
+  <si>
+    <t>Compared the checklist with the SQL Server project context and left database-specific query behavior for implementation review.</t>
+  </si>
+  <si>
+    <t>4 JDBC/DAO review points</t>
+  </si>
+  <si>
+    <t>Query syntax and transaction needs vary by operation and require verification against the real schema.</t>
+  </si>
+  <si>
+    <t>Peer Review 1 / Design Refinement</t>
+  </si>
+  <si>
+    <t>Organize database and JWT peer-review findings for design follow-up</t>
+  </si>
+  <si>
+    <t>Drafted a findings template with issue, affected ERD/token flow, severity, proposed change, and owner.</t>
+  </si>
+  <si>
+    <t>Matched the template to the Week 3 peer-review milestone; populate it with the team’s actual review results rather than assumed findings.</t>
+  </si>
+  <si>
+    <t>5 peer-review finding fields</t>
+  </si>
+  <si>
+    <t>No peer-review result is implied until reviewers complete and document the review.</t>
+  </si>
+  <si>
+    <t>Implementation / MVC2</t>
+  </si>
+  <si>
+    <t>Map the Submission Portal request flow across Controller, Service, DAO, and JSP layers</t>
+  </si>
+  <si>
+    <t>Drafted a submission workflow covering authenticated upload, server-side validation, persistence of submission metadata, and status display.</t>
+  </si>
+  <si>
+    <t>Compared the proposed layer responsibilities with the MVC2 pattern in the roadmap; actual class names and routes still need confirmation against the project.</t>
+  </si>
+  <si>
+    <t>4 MVC2 layers + 1 upload-to-history flow</t>
+  </si>
+  <si>
+    <t>The current repository structure and course/group ownership rules may require different controller, service, or DAO boundaries.</t>
+  </si>
+  <si>
+    <t>UI Development</t>
+  </si>
+  <si>
+    <t>Design a JSP submission-history view with JSTL and Expression Language</t>
+  </si>
+  <si>
+    <t>Drafted a JSP view to display the submitted file name, submission time, processing status, and feedback using JSTL and EL.</t>
+  </si>
+  <si>
+    <t>Checked the proposed fields against the Submission Portal workflow and kept rendering concerns in the View; model attribute names remain to be matched to the implementation.</t>
+  </si>
+  <si>
+    <t>1 JSP view + 4 submission-history fields</t>
+  </si>
+  <si>
+    <t>JSTL dependencies and backend attribute names are not verified in this draft.</t>
+  </si>
+  <si>
+    <t>Model submission records and artifact metadata for the portal</t>
+  </si>
+  <si>
+    <t>Suggested a SQL Server persistence design for student/group ownership, stored artifact metadata, status, timestamps, and a SHA-256 digest.</t>
+  </si>
+  <si>
+    <t>Compared the proposed fields with the portal requirements and noted that table and foreign-key names must follow the existing AITA schema.</t>
+  </si>
+  <si>
+    <t>1 submission record design + 5 metadata categories</t>
+  </si>
+  <si>
+    <t>The existing schema may already represent users, groups, or submissions differently; migration compatibility must be checked.</t>
+  </si>
+  <si>
+    <t>Implementation / Security</t>
+  </si>
+  <si>
+    <t>Specify multipart upload validation for ZIP submissions</t>
+  </si>
+  <si>
+    <t>Drafted server-side checks for request size, file extension, empty uploads, and ZIP readability before accepting a submission.</t>
+  </si>
+  <si>
+    <t>Reviewed the checks against the upload flow and separated file-type checks from later archive-content validation.</t>
+  </si>
+  <si>
+    <t>4 upload checks: size, extension, empty file, ZIP readability</t>
+  </si>
+  <si>
+    <t>File extension and MIME type alone do not establish that an archive is safe; size limits must also apply after extraction.</t>
   </si>
   <si>
     <t>Testing / Security</t>
   </si>
   <si>
-    <t>Create a Clean Code and Security testing checklist</t>
-  </si>
-  <si>
-    <t>Provided a checklist covering SQL Injection, XSS, Git API Token exposure, Authentication, Authorization, JDBC resource management, and input validation</t>
-  </si>
-  <si>
-    <t>Performed security checks and reviewed the code to identify and fix potential vulnerabilities</t>
-  </si>
-  <si>
-    <t>4 major security areas: SQL Injection, XSS, API Token, Access Control</t>
-  </si>
-  <si>
-    <t>A checklist provides guidance but does not replace professional penetration testing or a complete security audit</t>
-  </si>
-  <si>
-    <t>no1 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no2 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no3 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no4 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no5 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no6 and no6.1 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no7 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no8 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no9 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
-  </si>
-  <si>
-    <t>no10 of link drive https://drive.google.com/drive/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB?usp=sharing</t>
+    <t>Prepare boundary cases for the Submission Portal upload flow</t>
+  </si>
+  <si>
+    <t>Proposed cases for valid ZIPs, empty files, oversized requests, corrupt archives, path traversal entries, and unauthorized upload attempts.</t>
+  </si>
+  <si>
+    <t>Reviewed the cases against the stated portal risks and recorded them as a test plan; no test execution result is claimed here.</t>
+  </si>
+  <si>
+    <t>6 upload/security boundary-case categories</t>
+  </si>
+  <si>
+    <t>Expected status codes and project-specific maximum sizes must be confirmed before execution.</t>
+  </si>
+  <si>
+    <t>Implementation / File Integrity</t>
+  </si>
+  <si>
+    <t>Design server-side SHA-256 calculation for uploaded ZIP artifacts (4.4.2)</t>
+  </si>
+  <si>
+    <t>Outlined a Java MessageDigest approach to compute a SHA-256 digest from the uploaded file stream and store the resulting 64-character hexadecimal value.</t>
+  </si>
+  <si>
+    <t>Reviewed the server-side calculation flow and kept the uploaded bytes as the source of the digest; implementation and test results remain to be confirmed.</t>
+  </si>
+  <si>
+    <t>1 digest utility + 64-character hexadecimal output</t>
+  </si>
+  <si>
+    <t>A digest identifies file bytes but does not prove that the ZIP contents are safe.</t>
+  </si>
+  <si>
+    <t>Define the Filter gate for submission integrity checks</t>
+  </si>
+  <si>
+    <t>Drafted a Filter-to-Service flow that protects upload routes and prevents a submission from reaching persistence until server-side integrity validation completes.</t>
+  </si>
+  <si>
+    <t>Compared responsibilities with the Servlet Filter requirement and kept multipart parsing and digest calculation in the upload-processing layer where the file stream is available.</t>
+  </si>
+  <si>
+    <t>1 protected upload route + 1 integrity gate</t>
+  </si>
+  <si>
+    <t>A Filter cannot safely validate a digest unless the multipart request is parsed and the expected digest source is defined.</t>
+  </si>
+  <si>
+    <t>Security / File Integrity</t>
+  </si>
+  <si>
+    <t>Validate uploaded artifact bytes before saving the submission</t>
+  </si>
+  <si>
+    <t>Proposed calculating the digest during server-side processing and rejecting the submission if the bytes change between validation and persistence.</t>
+  </si>
+  <si>
+    <t>Reviewed the flow to ensure the server does not trust a client-supplied digest as proof of integrity.</t>
+  </si>
+  <si>
+    <t>1 server-side digest check + 1 persistence gate</t>
+  </si>
+  <si>
+    <t>Hash comparison is meaningful only when both compared values refer to the same byte stream and lifecycle.</t>
+  </si>
+  <si>
+    <t>Database / Implementation</t>
+  </si>
+  <si>
+    <t>Persist the artifact digest with submission metadata</t>
+  </si>
+  <si>
+    <t>Suggested storing the server-generated SHA-256 value with the submission record and using it for later integrity checks or duplicate warnings.</t>
+  </si>
+  <si>
+    <t>Checked that the digest is associated with the correct submission and group; duplicate handling should not block legitimate resubmission without a defined rule.</t>
+  </si>
+  <si>
+    <t>1 digest field + 1 submission association</t>
+  </si>
+  <si>
+    <t>A unique constraint on group and hash could reject valid repeated submissions or shared starter files.</t>
+  </si>
+  <si>
+    <t>Prepare boundary tests for ZIP and SHA-256 validation</t>
+  </si>
+  <si>
+    <t>Proposed cases for valid archives, corrupted ZIPs, invalid digest representation, changed bytes, oversized uploads, and rejected unauthenticated requests.</t>
+  </si>
+  <si>
+    <t>Reviewed the cases against the Week 4-6 upload and integrity objectives; the list is a test plan and does not claim tests were executed.</t>
+  </si>
+  <si>
+    <t>6 upload/integrity test categories</t>
+  </si>
+  <si>
+    <t>Expected responses, upload limits, and execution results must be recorded after testing in the target environment.</t>
+  </si>
+  <si>
+    <t>Peer Review / Architecture</t>
+  </si>
+  <si>
+    <t>Review the Submission Portal against the MVC2 separation of concerns</t>
+  </si>
+  <si>
+    <t>Created a review checklist tracing request handling from JSP through Controller, Service, DAO, and database.</t>
+  </si>
+  <si>
+    <t>Compared the checklist with the MVC2 defense objective and identified class ownership and validation placement as review points.</t>
+  </si>
+  <si>
+    <t>4 MVC2 layers + 1 end-to-end request trace</t>
+  </si>
+  <si>
+    <t>A checklist cannot establish that the implementation follows the design; source review is still required.</t>
+  </si>
+  <si>
+    <t>Peer Review / Security</t>
+  </si>
+  <si>
+    <t>Review Servlet Filter coverage for protected submission routes</t>
+  </si>
+  <si>
+    <t>Drafted a Filter review matrix for authentication, role authorization, URL mapping, upload routes, and rejection behavior.</t>
+  </si>
+  <si>
+    <t>Checked that the matrix covers both direct API access and browser navigation; actual filter mappings and security configuration remain to be verified.</t>
+  </si>
+  <si>
+    <t>5 Filter review areas</t>
+  </si>
+  <si>
+    <t>Incorrect URL mappings or relying on UI visibility can leave endpoints unprotected.</t>
+  </si>
+  <si>
+    <t>Review server-side SHA-256 verification for uploaded artifacts</t>
+  </si>
+  <si>
+    <t>Outlined the integrity flow: calculate SHA-256 from the received file on the server and compare it with the expected digest before persistence.</t>
+  </si>
+  <si>
+    <t>Compared the flow with the Week 5 hash entries and emphasized that the server-computed digest must be authoritative.</t>
+  </si>
+  <si>
+    <t>1 server-side digest + 1 comparison gate</t>
+  </si>
+  <si>
+    <t>A matching digest proves byte-level identity only when the expected digest is trusted; it does not establish that the archive is safe.</t>
+  </si>
+  <si>
+    <t>Define peer-review cases for ZIP validation and hash mismatch</t>
+  </si>
+  <si>
+    <t>Proposed checks for malformed ZIPs, traversal paths, size boundaries, invalid digest formats, and mismatched server-computed hashes.</t>
+  </si>
+  <si>
+    <t>Reviewed the cases against the Filter and integrity requirements and kept execution status open for the team to record after testing.</t>
+  </si>
+  <si>
+    <t>5 security test categories</t>
+  </si>
+  <si>
+    <t>Passing selected cases would not replace broader security review or resource-exhaustion testing.</t>
+  </si>
+  <si>
+    <t>Peer Review / Defense</t>
+  </si>
+  <si>
+    <t>Summarize MVC2 and Filter review findings for the Week 6 defense</t>
+  </si>
+  <si>
+    <t>Drafted a findings template linking each review observation to its affected layer, risk, proposed correction, and follow-up check.</t>
+  </si>
+  <si>
+    <t>Aligned the template with the defense topics in the roadmap; findings should be populated from the actual peer review.</t>
+  </si>
+  <si>
+    <t>4 review fields: layer, finding, correction, follow-up</t>
+  </si>
+  <si>
+    <t>This is a review aid; it does not represent completed peer-review findings.</t>
+  </si>
+  <si>
+    <t>AI Integration / Architecture</t>
+  </si>
+  <si>
+    <t>Design a provider abstraction for OpenAI and Gemini grading calls</t>
+  </si>
+  <si>
+    <t>Drafted a provider interface and configuration approach for OpenAI/Gemini requests, with prompt inputs separated from provider-specific transport.</t>
+  </si>
+  <si>
+    <t>Compared the design with the roadmap and kept credentials in environment configuration; the actual provider choice and API contract need confirmation.</t>
+  </si>
+  <si>
+    <t>2 provider options + 1 provider abstraction</t>
+  </si>
+  <si>
+    <t>API availability, model behavior, rate limits, and response formats may change and require live integration checks.</t>
+  </si>
+  <si>
+    <t>Database / JPA-ORM</t>
+  </si>
+  <si>
+    <t>Model Git repositories, commits, and contribution scores with JPA entities</t>
+  </si>
+  <si>
+    <t>Suggested JPA entity relationships for repository ownership, commit attribution, and per-student contribution results.</t>
+  </si>
+  <si>
+    <t>Reviewed the entity boundaries against FE-L-03 data needs and flagged that they must map to the existing SQL Server schema.</t>
+  </si>
+  <si>
+    <t>3 core entity types + relationship mappings</t>
+  </si>
+  <si>
+    <t>The current project documentation describes JDBC and SQL Server; adopting JPA may require dependency, transaction, and migration changes.</t>
+  </si>
+  <si>
+    <t>Business Logic / Git Analytics</t>
+  </si>
+  <si>
+    <t>Structure the contribution-scoring pipeline for FE-L-03</t>
+  </si>
+  <si>
+    <t>Drafted calculation stages for LOC volume, activity regularity, review interaction, penalties, normalized percentages, and free-rider flags.</t>
+  </si>
+  <si>
+    <t>Compared the stages with the Git Analytics report model and kept scoring weights configurable rather than embedding them in entity code.</t>
+  </si>
+  <si>
+    <t>4 scoring dimensions + normalization + 2 warning criteria</t>
+  </si>
+  <si>
+    <t>Git metrics can misrepresent work quality, and score normalization needs safeguards when group totals are zero or negative.</t>
+  </si>
+  <si>
+    <t>Background Jobs / JPA</t>
+  </si>
+  <si>
+    <t>Design a persistent grading-job record and lifecycle</t>
+  </si>
+  <si>
+    <t>Proposed a JPA job model with submission reference, status, priority, attempt count, timestamps, and failure summary.</t>
+  </si>
+  <si>
+    <t>Checked that the job record supports retry visibility and idempotent processing; persistence behavior still needs implementation review.</t>
+  </si>
+  <si>
+    <t>1 job entity + 6 lifecycle fields</t>
+  </si>
+  <si>
+    <t>A database record alone does not provide queue delivery guarantees or prevent duplicate worker execution.</t>
+  </si>
+  <si>
+    <t>Background Jobs / Redis</t>
+  </si>
+  <si>
+    <t>Specify priority and retry behavior for the grading queue</t>
+  </si>
+  <si>
+    <t>Drafted priority ordering and bounded retry with backoff, terminal failure handling, and a link from Redis jobs to persistent JPA job records.</t>
+  </si>
+  <si>
+    <t>Reviewed the design against the concurrent-submission objective and kept the database as the durable source of job status.</t>
+  </si>
+  <si>
+    <t>1 priority policy + bounded retries + 1 durable status record</t>
+  </si>
+  <si>
+    <t>Redis persistence, duplicate delivery, worker crashes, and retry storms need explicit operational handling.</t>
+  </si>
+  <si>
+    <t>Sandbox / Security</t>
+  </si>
+  <si>
+    <t>Define Docker resource limits for automated grading</t>
+  </si>
+  <si>
+    <t>Outlined container limits for execution time, memory, CPU, and process count, with network access disabled for untrusted submissions.</t>
+  </si>
+  <si>
+    <t>Compared the controls with the roadmap requirement for strict time and memory limits; numeric thresholds must be set from the course specification and host capacity.</t>
+  </si>
+  <si>
+    <t>4 resource controls + network isolation</t>
+  </si>
+  <si>
+    <t>Container limits and isolation strength depend on the Docker/runtime configuration and require security review.</t>
+  </si>
+  <si>
+    <t>Sandbox / Artifact Processing</t>
+  </si>
+  <si>
+    <t>Prepare ZIP source files for isolated sandbox execution</t>
+  </si>
+  <si>
+    <t>Drafted a safe extraction flow with path normalization, archive-entry checks, file-count and expanded-size caps, and temporary workspace cleanup.</t>
+  </si>
+  <si>
+    <t>Reviewed the flow against the prior ZIP/Zip Slip requirements and kept extraction separate from grading execution.</t>
+  </si>
+  <si>
+    <t>4 archive safeguards + 1 temporary workspace lifecycle</t>
+  </si>
+  <si>
+    <t>Ignored-directory rules can omit required files; compressed-size limits alone do not prevent ZIP bombs.</t>
+  </si>
+  <si>
+    <t>AI Integration / Background Jobs</t>
+  </si>
+  <si>
+    <t>Connect the grading worker to the AI provider through the job queue</t>
+  </si>
+  <si>
+    <t>Proposed a worker flow to load a queued job, collect sandbox results, call the configured AI provider with a timeout, and update job status.</t>
+  </si>
+  <si>
+    <t>Checked that provider calls occur outside the web request path and that secrets are excluded from logs; actual API and queue behavior still need testing.</t>
+  </si>
+  <si>
+    <t>1 asynchronous worker flow + 1 provider timeout</t>
+  </si>
+  <si>
+    <t>Provider outages, throttling, long responses, and malformed output can delay or fail grading jobs.</t>
+  </si>
+  <si>
+    <t>Business Logic / Results</t>
+  </si>
+  <si>
+    <t>Validate and persist AI grading output for the Git Analytics dashboard</t>
+  </si>
+  <si>
+    <t>Drafted result checks for required score fields, bounded values, feedback text, and association with the correct student, group, and job.</t>
+  </si>
+  <si>
+    <t>Compared the result shape with FE-L-03 dashboard needs and kept invalid or incomplete responses from being treated as final scores.</t>
+  </si>
+  <si>
+    <t>4 output validation groups</t>
+  </si>
+  <si>
+    <t>AI-generated feedback may be inconsistent; lecturer review and transparent score explanations remain necessary.</t>
+  </si>
+  <si>
+    <t>Integration Testing / Security</t>
+  </si>
+  <si>
+    <t>Prepare end-to-end checks for queue, sandbox, and contribution scoring</t>
+  </si>
+  <si>
+    <t>Proposed scenarios for concurrent jobs, retry after provider failure, timeout, memory-limit termination, malformed output, and score persistence.</t>
+  </si>
+  <si>
+    <t>Reviewed the scenarios against the Week 7-8 integration scope and recorded them as planned checks rather than completed test results.</t>
+  </si>
+  <si>
+    <t>6 integration/failure scenarios</t>
+  </si>
+  <si>
+    <t>Load and isolation properties cannot be confirmed without running tests in the target deployment environment.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/u/2/folders/144TvYTVbl6N4-PbTLWSXEX2D0Lv2uQdB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,8 +940,19 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,7 +981,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,10 +1047,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -569,17 +1081,29 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -593,8 +1117,24 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -834,99 +1374,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -1042,6 +1582,108 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1095,7 +1737,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1114,145 +1756,145 @@
       <c r="F2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>117</v>
+      <c r="G2" s="25" t="s">
+        <v>289</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>62</v>
       </c>
       <c r="I2" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>118</v>
+        <v>67</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>289</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I3" s="5">
         <v>5</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>119</v>
+        <v>73</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>289</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I4" s="5">
         <v>5</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>120</v>
+        <v>79</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>289</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>121</v>
+        <v>85</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>289</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I6" s="5">
         <v>5</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1398,6 +2040,13 @@
       <c r="J30" s="7"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{2FC0BCE0-F38D-42B4-8322-F0DFB58AA3F6}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{89B1E875-2FD4-4764-985E-54B22B52937F}"/>
+    <hyperlink ref="G5" r:id="rId3" xr:uid="{996FB65D-619C-4BF8-A484-D20F85B64D2A}"/>
+    <hyperlink ref="G4" r:id="rId4" xr:uid="{5C69676F-0094-4EFB-9A12-331BF294EAB7}"/>
+    <hyperlink ref="G3" r:id="rId5" xr:uid="{470AA829-BE0E-4DC1-9EEA-FC53082A6DA8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1451,269 +2100,1500 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11">
+    <row r="2" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
         <v>6</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="12" t="s">
+      <c r="D2" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
+        <v>4</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
+        <v>7</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="13">
+        <v>4</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15">
+        <v>8</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" s="15">
         <v>5</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
-        <v>7</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="11">
-        <v>5</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14">
-        <v>8</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="I4" s="14">
-        <v>5</v>
-      </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+    <row r="5" spans="1:10" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15">
         <v>9</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="G5" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="H5" s="13" t="s">
+      <c r="I5" s="15">
+        <v>4</v>
+      </c>
+      <c r="J5" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I5" s="14">
-        <v>5</v>
-      </c>
-      <c r="J5" s="13" t="s">
+    </row>
+    <row r="6" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15">
+        <v>10</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
-        <v>10</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="D6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="F6" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="G6" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="I6" s="15">
+        <v>4</v>
+      </c>
+      <c r="J6" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="I6" s="14">
-        <v>5</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>116</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{B0369FD2-198C-4FE9-AA54-58934AE68277}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{3AF3D07D-7279-49F4-9FD6-52D034734D47}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{2FE6611D-3832-455E-BDAC-86EC1C938206}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{9D5888D4-FF7F-4CDD-93F9-383CAC75FEAD}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{4A443DCC-AE13-4D0A-B047-F1E7FC975F21}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="C1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="D1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="E1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="F1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="G1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="H1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="I1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="J1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>56</v>
+    </row>
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
+        <v>11</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="17">
+        <v>5</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>12</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="17">
+        <v>5</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
+        <v>13</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="I4" s="17">
+        <v>4</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>14</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="17">
+        <v>4</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17">
+        <v>15</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I6" s="17">
+        <v>4</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{C4434EA4-723A-4C5E-B91D-3D11891A1E37}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{2F39B1A8-5379-4849-9318-4C973A2CE4B7}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{4B41E4B0-B4AE-475B-A719-F049CCD81ABD}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{014369DA-DFEA-4F44-9D1C-6709636050D6}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{96EADB28-500C-4133-A006-055A1DD7A3C6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>21</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I2" s="5">
+        <v>4</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>22</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>23</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>24</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I5" s="5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{3DA9EB80-87EB-4549-98F2-4A01D95FBBA0}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{A25D75A7-AA00-49FC-88C4-91D36E088761}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{9E278C12-AAAD-4A6B-BEDB-08E8AD0897F8}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{909F96C1-FF6C-41EB-B7F0-34D091BC0AB7}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{07927EC7-9200-47E4-8E63-EBA1D49A4FFE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
+        <v>16</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="17">
+        <v>5</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>17</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="I3" s="17">
+        <v>4</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
+        <v>18</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="17">
+        <v>5</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>19</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="I5" s="17">
+        <v>4</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17">
+        <v>20</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="I6" s="17">
+        <v>4</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{3B66B38B-18E6-448D-90E9-13CC7D8676FE}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{79CFD0CD-5426-4230-853B-71DB8CB68FF3}"/>
+    <hyperlink ref="G5" r:id="rId3" xr:uid="{05BD0940-00F9-4813-B08F-F5B81269A88E}"/>
+    <hyperlink ref="G4" r:id="rId4" xr:uid="{A7DD373C-D1E5-4F46-BDCC-0989AED822C4}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{665D9C82-BAFD-4C6A-97A2-2BBB8EAB2C12}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>26</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="I2" s="5">
+        <v>5</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>27</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>28</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I4" s="5">
+        <v>5</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>29</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>30</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{7BBA8C95-4EFE-468D-B899-CD70E6B7EF38}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{97E8CD6A-CCB1-4D2B-A4E6-85EC0135DDE8}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{8AAA43BD-6AFB-4A7A-921B-3D76E28D8CA3}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{F2F28EA5-A7E0-44B8-857E-A79F84B05D73}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{163EB5AC-5643-4E04-80A1-2DF21A1D6573}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>31</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I2" s="5">
+        <v>4</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>32</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>33</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I4" s="5">
+        <v>5</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>34</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>35</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{26450C3B-8024-4B31-B9F9-643D236F4C15}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{23757EF5-3E5A-4C9A-A367-8402C03C2F19}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{734AFD0B-73F2-4052-9176-2DE63C10A6B2}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{26636C14-7724-414F-84C6-5FB1B363AE68}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{C313C768-865E-4D0B-9B9F-5C46BC7573DD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>36</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I2" s="5">
+        <v>5</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>37</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>38</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>39</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>40</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{0C7DC042-1272-41C3-958D-0B21E65790FD}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{D197C1FA-C81C-4337-951F-E71115F973DF}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{52454B79-7FDD-4208-B174-8F5F45744ACA}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{DF3409C4-FE0A-4BFE-A069-3570C19F554C}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{C9600FE3-5D98-4690-954D-9AFAB7FDFF4F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>